--- a/Diccionario_Datos_Heladeria-2.xlsx
+++ b/Diccionario_Datos_Heladeria-2.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="184">
   <si>
     <t xml:space="preserve">Tabla</t>
   </si>
@@ -469,52 +469,76 @@
     <t xml:space="preserve">Nombre del sabor o producto.</t>
   </si>
   <si>
+    <t xml:space="preserve">precio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio del producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">es_vegano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define si es apto para veganos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">receta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEXT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingredientes y pasos de preparación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lote_producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_lote_producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">si</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificador único de detalle_producto</t>
+  </si>
+  <si>
     <t xml:space="preserve">stock</t>
   </si>
   <si>
-    <t xml:space="preserve">Cantidad disponible en inventario.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">es_vegano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Define si es apto para veganos.</t>
+    <t xml:space="preserve">El stock del lote</t>
   </si>
   <si>
     <t xml:space="preserve">fecha_elaboracion</t>
   </si>
   <si>
-    <t xml:space="preserve">Fecha en que se fabricó el helado.</t>
+    <t xml:space="preserve">Fecha  en la cual se elaboro el producto</t>
   </si>
   <si>
     <t xml:space="preserve">fecha_vencimiento</t>
   </si>
   <si>
-    <t xml:space="preserve">Fecha máxima para consumo.</t>
+    <t xml:space="preserve">Fecha en la cual vence el producto</t>
   </si>
   <si>
     <t xml:space="preserve">fecha_salida_sala</t>
   </si>
   <si>
-    <t xml:space="preserve">Fecha en que el producto se puso a la venta.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">receta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEXT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingredientes y pasos de preparación.</t>
+    <t xml:space="preserve">Fecha  en la cual salio el producto a sala</t>
   </si>
   <si>
     <t xml:space="preserve">id_maquina</t>
   </si>
   <si>
-    <t xml:space="preserve">Maquina.id_maquina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Máquina donde se elaboró.</t>
+    <t xml:space="preserve">maquina.id_maquina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificador único de que maquina lo produce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificador único de que producto es el lote</t>
   </si>
   <si>
     <t xml:space="preserve">Maquina</t>
@@ -563,7 +587,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -583,9 +606,9 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -715,14 +738,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -730,58 +753,25 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
+          <a:miter/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -799,48 +789,12 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
@@ -852,7 +806,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
@@ -864,7 +818,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -890,7 +844,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -916,7 +870,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -942,7 +896,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -968,7 +922,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -994,7 +948,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1020,7 +974,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
@@ -1046,7 +1000,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>25</v>
       </c>
@@ -1072,7 +1026,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -1098,7 +1052,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -1124,7 +1078,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>25</v>
       </c>
@@ -1144,13 +1098,13 @@
         <v>34</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
@@ -1176,7 +1130,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
@@ -1202,7 +1156,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>36</v>
       </c>
@@ -1228,7 +1182,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>36</v>
       </c>
@@ -1254,7 +1208,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>36</v>
       </c>
@@ -1280,7 +1234,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>48</v>
       </c>
@@ -1306,7 +1260,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
@@ -1332,7 +1286,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>48</v>
       </c>
@@ -1358,7 +1312,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>48</v>
       </c>
@@ -1384,7 +1338,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>48</v>
       </c>
@@ -1410,7 +1364,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -1436,7 +1390,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>48</v>
       </c>
@@ -1462,7 +1416,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>48</v>
       </c>
@@ -1488,7 +1442,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>65</v>
       </c>
@@ -1514,7 +1468,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>65</v>
       </c>
@@ -1540,7 +1494,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>65</v>
       </c>
@@ -1566,7 +1520,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>65</v>
       </c>
@@ -1592,7 +1546,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>65</v>
       </c>
@@ -1618,7 +1572,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>65</v>
       </c>
@@ -1644,7 +1598,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>65</v>
       </c>
@@ -1670,7 +1624,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>80</v>
       </c>
@@ -1696,7 +1650,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>80</v>
       </c>
@@ -1722,7 +1676,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>80</v>
       </c>
@@ -1748,7 +1702,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>80</v>
       </c>
@@ -1774,7 +1728,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>80</v>
       </c>
@@ -1800,7 +1754,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>91</v>
       </c>
@@ -1826,7 +1780,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>91</v>
       </c>
@@ -1852,7 +1806,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>91</v>
       </c>
@@ -1878,7 +1832,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>91</v>
       </c>
@@ -1904,7 +1858,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>91</v>
       </c>
@@ -1930,7 +1884,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>91</v>
       </c>
@@ -1956,7 +1910,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>102</v>
       </c>
@@ -1982,7 +1936,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>102</v>
       </c>
@@ -2008,7 +1962,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>102</v>
       </c>
@@ -2034,7 +1988,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>102</v>
       </c>
@@ -2060,7 +2014,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>102</v>
       </c>
@@ -2086,7 +2040,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>102</v>
       </c>
@@ -2112,7 +2066,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>102</v>
       </c>
@@ -2138,7 +2092,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
         <v>102</v>
       </c>
@@ -2164,7 +2118,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
         <v>119</v>
       </c>
@@ -2190,7 +2144,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
         <v>119</v>
       </c>
@@ -2216,7 +2170,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
         <v>119</v>
       </c>
@@ -2242,7 +2196,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>119</v>
       </c>
@@ -2268,7 +2222,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
         <v>119</v>
       </c>
@@ -2294,7 +2248,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
         <v>119</v>
       </c>
@@ -2320,7 +2274,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
         <v>119</v>
       </c>
@@ -2346,7 +2300,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
         <v>119</v>
       </c>
@@ -2373,7 +2327,7 @@
       </c>
       <c r="I58" s="1"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
         <v>136</v>
       </c>
@@ -2399,7 +2353,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
         <v>136</v>
       </c>
@@ -2425,7 +2379,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
         <v>136</v>
       </c>
@@ -2451,7 +2405,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
         <v>136</v>
       </c>
@@ -2477,7 +2431,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
         <v>146</v>
       </c>
@@ -2503,7 +2457,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
         <v>146</v>
       </c>
@@ -2529,7 +2483,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>146</v>
       </c>
@@ -2540,27 +2494,27 @@
         <v>21</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
         <v>146</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>74</v>
@@ -2578,293 +2532,371 @@
         <v>11</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
         <v>146</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C67" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C68" s="1" t="s">
+      <c r="D70" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B69" s="1" t="s">
+      <c r="D71" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="B72" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B70" s="1" t="s">
+      <c r="D72" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C71" s="1" t="s">
+      <c r="F73" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C72" s="1" t="s">
+      <c r="D74" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C73" s="1" t="s">
+      <c r="D75" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C74" s="1" t="s">
+      <c r="D76" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C75" s="1" t="s">
+      <c r="D77" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B76" s="1" t="s">
+      <c r="D78" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="B79" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B77" s="1" t="s">
+      <c r="D79" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D77" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E77" s="1" t="s">
+      <c r="D80" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="F80" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="G80" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H77" s="1" t="s">
-        <v>175</v>
+      <c r="H80" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/Diccionario_Datos_Heladeria-2.xlsx
+++ b/Diccionario_Datos_Heladeria-2.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="186">
   <si>
     <t xml:space="preserve">Tabla</t>
   </si>
@@ -503,6 +503,12 @@
   </si>
   <si>
     <t xml:space="preserve">Identificador único de detalle_producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coste_lote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coste del lote</t>
   </si>
   <si>
     <t xml:space="preserve">stock</t>
@@ -581,12 +587,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -605,6 +612,13 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -666,7 +680,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -680,6 +694,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -806,7 +824,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
@@ -818,7 +836,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -844,7 +862,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -870,7 +888,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -896,7 +914,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -922,7 +940,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -948,7 +966,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -974,7 +992,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
@@ -1000,7 +1018,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>25</v>
       </c>
@@ -1026,7 +1044,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -1052,7 +1070,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -1078,7 +1096,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>25</v>
       </c>
@@ -1104,7 +1122,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
@@ -1130,7 +1148,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
@@ -1156,7 +1174,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>36</v>
       </c>
@@ -1182,7 +1200,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>36</v>
       </c>
@@ -1208,7 +1226,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>36</v>
       </c>
@@ -1234,7 +1252,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>48</v>
       </c>
@@ -1260,7 +1278,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
@@ -1286,7 +1304,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>48</v>
       </c>
@@ -1312,7 +1330,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>48</v>
       </c>
@@ -1338,7 +1356,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>48</v>
       </c>
@@ -1364,7 +1382,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -1390,7 +1408,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>48</v>
       </c>
@@ -1416,7 +1434,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>48</v>
       </c>
@@ -1442,7 +1460,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>65</v>
       </c>
@@ -1468,7 +1486,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>65</v>
       </c>
@@ -1494,7 +1512,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>65</v>
       </c>
@@ -1520,7 +1538,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>65</v>
       </c>
@@ -1546,7 +1564,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>65</v>
       </c>
@@ -1572,7 +1590,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>65</v>
       </c>
@@ -1598,7 +1616,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>65</v>
       </c>
@@ -1624,7 +1642,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>80</v>
       </c>
@@ -1650,7 +1668,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>80</v>
       </c>
@@ -1676,7 +1694,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>80</v>
       </c>
@@ -1702,7 +1720,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>80</v>
       </c>
@@ -1728,7 +1746,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>80</v>
       </c>
@@ -1754,7 +1772,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>91</v>
       </c>
@@ -1780,7 +1798,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>91</v>
       </c>
@@ -1806,7 +1824,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>91</v>
       </c>
@@ -1832,7 +1850,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>91</v>
       </c>
@@ -1858,7 +1876,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>91</v>
       </c>
@@ -1884,7 +1902,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>91</v>
       </c>
@@ -1910,7 +1928,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>102</v>
       </c>
@@ -1936,7 +1954,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>102</v>
       </c>
@@ -1962,7 +1980,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>102</v>
       </c>
@@ -1988,7 +2006,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>102</v>
       </c>
@@ -2014,7 +2032,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>102</v>
       </c>
@@ -2040,7 +2058,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>102</v>
       </c>
@@ -2066,7 +2084,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>102</v>
       </c>
@@ -2092,7 +2110,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
         <v>102</v>
       </c>
@@ -2118,7 +2136,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
         <v>119</v>
       </c>
@@ -2144,7 +2162,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
         <v>119</v>
       </c>
@@ -2170,7 +2188,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
         <v>119</v>
       </c>
@@ -2196,7 +2214,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>119</v>
       </c>
@@ -2222,7 +2240,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
         <v>119</v>
       </c>
@@ -2248,7 +2266,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
         <v>119</v>
       </c>
@@ -2274,7 +2292,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
         <v>119</v>
       </c>
@@ -2300,7 +2318,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
         <v>119</v>
       </c>
@@ -2327,7 +2345,7 @@
       </c>
       <c r="I58" s="1"/>
     </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
         <v>136</v>
       </c>
@@ -2353,7 +2371,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
         <v>136</v>
       </c>
@@ -2379,7 +2397,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
         <v>136</v>
       </c>
@@ -2405,7 +2423,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
         <v>136</v>
       </c>
@@ -2431,7 +2449,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
         <v>146</v>
       </c>
@@ -2457,7 +2475,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
         <v>146</v>
       </c>
@@ -2483,7 +2501,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>146</v>
       </c>
@@ -2509,7 +2527,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
         <v>146</v>
       </c>
@@ -2535,7 +2553,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
         <v>146</v>
       </c>
@@ -2561,7 +2579,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
         <v>157</v>
       </c>
@@ -2587,11 +2605,11 @@
         <v>160</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="4" t="s">
         <v>161</v>
       </c>
       <c r="C69" s="1" t="s">
@@ -2613,15 +2631,15 @@
         <v>162</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="1" t="s">
         <v>163</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>150</v>
@@ -2639,11 +2657,11 @@
         <v>164</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="3" t="s">
         <v>165</v>
       </c>
       <c r="C71" s="1" t="s">
@@ -2665,7 +2683,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
         <v>157</v>
       </c>
@@ -2685,13 +2703,13 @@
         <v>13</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>157</v>
       </c>
@@ -2699,30 +2717,30 @@
         <v>169</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>150</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="F73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H73" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G73" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
         <v>157</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>21</v>
@@ -2734,53 +2752,53 @@
         <v>159</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>159</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>11</v>
+        <v>150</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>12</v>
@@ -2795,15 +2813,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>177</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>12</v>
@@ -2821,15 +2839,15 @@
         <v>178</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>179</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>12</v>
@@ -2841,21 +2859,21 @@
         <v>13</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>181</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>12</v>
@@ -2873,30 +2891,56 @@
         <v>182</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B80" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E80" s="1" t="s">
+      <c r="D81" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F81" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G80" s="1" t="s">
+      <c r="G81" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H80" s="1" t="s">
-        <v>183</v>
+      <c r="H81" s="1" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/Diccionario_Datos_Heladeria-2.xlsx
+++ b/Diccionario_Datos_Heladeria-2.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="187">
   <si>
     <t xml:space="preserve">Tabla</t>
   </si>
@@ -445,103 +445,106 @@
     <t xml:space="preserve">Boleta a la que pertenece el producto.</t>
   </si>
   <si>
+    <t xml:space="preserve">id_lote_producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lote_producto.id_lote_producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lote al que pertenece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cantidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantidad de unidades del producto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Producto</t>
+  </si>
+  <si>
     <t xml:space="preserve">id_producto</t>
   </si>
   <si>
+    <t xml:space="preserve">Identificador único del helado o insumo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre del sabor o producto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">precio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio del producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">es_vegano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define si es apto para veganos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">receta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEXT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingredientes y pasos de preparación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lote_producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">si</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificador único de detalle_producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coste_lote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coste del lote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El stock del lote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fecha_elaboracion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha  en la cual se elaboro el producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fecha_vencimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha en la cual vence el producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fecha_salida_sala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha  en la cual salio el producto a sala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_maquina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maquina.id_maquina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificador único de que maquina lo produce</t>
+  </si>
+  <si>
     <t xml:space="preserve">Producto.id_producto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producto vendido.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cantidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cantidad de unidades del producto.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identificador único del helado o insumo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre del sabor o producto.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">precio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Precio del producto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">es_vegano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Define si es apto para veganos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">receta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEXT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingredientes y pasos de preparación.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lote_producto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id_lote_producto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">si</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identificador único de detalle_producto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coste_lote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coste del lote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El stock del lote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fecha_elaboracion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha  en la cual se elaboro el producto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fecha_vencimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha en la cual vence el producto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fecha_salida_sala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha  en la cual salio el producto a sala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id_maquina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maquina.id_maquina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identificador único de que maquina lo produce</t>
   </si>
   <si>
     <t xml:space="preserve">Identificador único de que producto es el lote</t>
@@ -587,7 +590,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -617,12 +620,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -680,7 +677,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -694,10 +691,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2454,7 +2447,7 @@
         <v>146</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>10</v>
@@ -2472,7 +2465,7 @@
         <v>11</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2498,7 +2491,7 @@
         <v>11</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2506,16 +2499,16 @@
         <v>146</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>13</v>
@@ -2524,7 +2517,7 @@
         <v>83</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2532,7 +2525,7 @@
         <v>146</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>74</v>
@@ -2550,7 +2543,7 @@
         <v>11</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2558,10 +2551,10 @@
         <v>146</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>12</v>
@@ -2576,15 +2569,15 @@
         <v>12</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>10</v>
@@ -2593,7 +2586,7 @@
         <v>159</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>13</v>
@@ -2607,19 +2600,19 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B69" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>161</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>13</v>
@@ -2633,7 +2626,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>163</v>
@@ -2642,10 +2635,10 @@
         <v>21</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>13</v>
@@ -2659,7 +2652,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>165</v>
@@ -2668,10 +2661,10 @@
         <v>53</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>13</v>
@@ -2685,7 +2678,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>167</v>
@@ -2694,10 +2687,10 @@
         <v>53</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>13</v>
@@ -2711,7 +2704,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>169</v>
@@ -2720,16 +2713,16 @@
         <v>53</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>170</v>
@@ -2737,7 +2730,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>171</v>
@@ -2746,7 +2739,7 @@
         <v>21</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>159</v>
@@ -2763,33 +2756,33 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>159</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>159</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>171</v>
@@ -2810,15 +2803,15 @@
         <v>11</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>53</v>
@@ -2836,15 +2829,15 @@
         <v>11</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>74</v>
@@ -2862,15 +2855,15 @@
         <v>11</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>16</v>
@@ -2888,15 +2881,15 @@
         <v>12</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>111</v>
@@ -2914,12 +2907,12 @@
         <v>12</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>9</v>
@@ -2940,7 +2933,7 @@
         <v>83</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/Diccionario_Datos_Heladeria-2.xlsx
+++ b/Diccionario_Datos_Heladeria-2.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="194">
   <si>
     <t xml:space="preserve">Tabla</t>
   </si>
@@ -352,6 +352,18 @@
     <t xml:space="preserve">Define si la caja está operativa (true) o cerrada (false).</t>
   </si>
   <si>
+    <t xml:space="preserve">detalle_caja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_detalle_caja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificador único de detalle de la caja</t>
+  </si>
+  <si>
     <t xml:space="preserve">monto_apertura</t>
   </si>
   <si>
@@ -373,12 +385,27 @@
     <t xml:space="preserve">Empleado encargado de abrir/cerrar la caja.</t>
   </si>
   <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha del detalle</t>
+  </si>
+  <si>
     <t xml:space="preserve">transacciones_del_dia</t>
   </si>
   <si>
+    <t xml:space="preserve">NO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Contador de ventas realizadas en el día.</t>
   </si>
   <si>
+    <t xml:space="preserve">si</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificador único de la caja a la que pertenece el detalle</t>
+  </si>
+  <si>
     <t xml:space="preserve">Transaccion</t>
   </si>
   <si>
@@ -475,9 +502,6 @@
     <t xml:space="preserve">precio</t>
   </si>
   <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
     <t xml:space="preserve">Precio del producto</t>
   </si>
   <si>
@@ -497,9 +521,6 @@
   </si>
   <si>
     <t xml:space="preserve">lote_producto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">si</t>
   </si>
   <si>
     <t xml:space="preserve">Identificador único de detalle_producto</t>
@@ -590,7 +611,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -620,6 +641,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -677,7 +704,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -691,6 +718,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -817,7 +848,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
@@ -2027,16 +2058,16 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>12</v>
@@ -2048,18 +2079,18 @@
         <v>11</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>12</v>
@@ -2074,41 +2105,41 @@
         <v>12</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="D49" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>21</v>
@@ -2117,50 +2148,50 @@
         <v>12</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
-        <v>119</v>
+      <c r="A51" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>11</v>
+        <v>112</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>21</v>
@@ -2169,24 +2200,24 @@
         <v>12</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>21</v>
@@ -2195,131 +2226,131 @@
         <v>12</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>11</v>
+        <v>126</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>125</v>
+        <v>13</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>13</v>
+        <v>134</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>12</v>
@@ -2334,22 +2365,22 @@
         <v>11</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I58" s="1"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>12</v>
@@ -2361,73 +2392,73 @@
         <v>11</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>21</v>
+        <v>142</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>143</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>12</v>
@@ -2439,99 +2470,99 @@
         <v>11</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>13</v>
+        <v>148</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>151</v>
+        <v>12</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>151</v>
+        <v>12</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>12</v>
@@ -2543,18 +2574,18 @@
         <v>11</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>155</v>
+        <v>30</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>156</v>
+        <v>16</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>12</v>
@@ -2566,33 +2597,33 @@
         <v>13</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>160</v>
@@ -2600,25 +2631,25 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B69" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>161</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>151</v>
+        <v>12</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>151</v>
+        <v>12</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>159</v>
+        <v>11</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>162</v>
@@ -2626,129 +2657,129 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>163</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>151</v>
+        <v>12</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>151</v>
+        <v>12</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>173</v>
@@ -2756,25 +2787,25 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>174</v>
+        <v>13</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>175</v>
@@ -2782,25 +2813,25 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="C76" s="1" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>177</v>
@@ -2808,68 +2839,68 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>178</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>12</v>
+        <v>126</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>13</v>
+        <v>179</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>11</v>
+        <v>126</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>12</v>
+        <v>126</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>13</v>
+        <v>181</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>11</v>
+        <v>126</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>12</v>
@@ -2878,21 +2909,21 @@
         <v>13</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>111</v>
+        <v>53</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>12</v>
@@ -2904,36 +2935,114 @@
         <v>13</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B81" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E81" s="1" t="s">
+      <c r="D84" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F84" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G81" s="1" t="s">
+      <c r="G84" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H81" s="1" t="s">
-        <v>186</v>
+      <c r="H84" s="1" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
